--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -5095,7 +5095,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>동양생명</t>
+          <t>동양생명보험</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7146,7 +7146,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>세아메카닉스</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -24920,7 +24920,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>코윈테크</t>
+          <t>코윈로보틱스</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -3648,7 +3648,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>국일제지</t>
+          <t>에스엠국일</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -24503,7 +24503,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>캔버스엔</t>
+          <t>빅텐츠</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -25241,7 +25241,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>탑코미디어</t>
+          <t>엔키AX</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">

--- a/시그널뷰_관련테마.xlsx
+++ b/시그널뷰_관련테마.xlsx
@@ -2664,7 +2664,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S&amp;K폴리텍</t>
+          <t>S&amp;K글로벌</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>동아쏘시오홀딩스</t>
+          <t>동아제약</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -22002,7 +22002,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
